--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484295_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484295_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2201</v>
+        <v>8.922800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0295</v>
+        <v>6.7867</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1905</v>
+        <v>2.1361</v>
       </c>
       <c r="G2" t="n">
         <v>6.7099</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5222</v>
+        <v>0.2249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5009</v>
+        <v>0.2581</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0213</v>
+        <v>-0.0332</v>
       </c>
       <c r="V2" t="n">
         <v>2.7693</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8117</v>
+        <v>2.9215</v>
       </c>
       <c r="E3" t="n">
-        <v>5.432</v>
+        <v>3.8142</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6204</v>
+        <v>-0.8927</v>
       </c>
       <c r="G3" t="n">
         <v>4.8511</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7623</v>
+        <v>0.8722</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5837</v>
+        <v>0.9659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1786</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-0.067</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0968</v>
+        <v>2.5391</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2535</v>
+        <v>1.4477</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8433</v>
+        <v>1.0914</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6065</v>
+        <v>2.3842</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6488</v>
+        <v>0.7391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9578</v>
+        <v>1.6451</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6166</v>
+        <v>3.0835</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3888</v>
+        <v>0.4937</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2278</v>
+        <v>2.5898</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0101</v>
+        <v>-0.6994</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2599</v>
+        <v>0.2454</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.27</v>
+        <v>-0.9447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2911</v>
+        <v>0.1912</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3631</v>
+        <v>0.3454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.1542</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2316</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6914</v>
+        <v>2.2778</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4365</v>
+        <v>1.5163</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2548</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3842</v>
+        <v>1.6065</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7391</v>
+        <v>0.6488</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6451</v>
+        <v>0.9578</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0835</v>
+        <v>1.6166</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4937</v>
+        <v>0.3888</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5898</v>
+        <v>1.2278</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6994</v>
+        <v>-0.0101</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2454</v>
+        <v>0.2599</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9447</v>
+        <v>-0.27</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6566</v>
+        <v>-0.1101</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6657</v>
+        <v>-0.1004</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0092</v>
+        <v>-0.0097</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2316</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8879</v>
+        <v>1.0735</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3676</v>
+        <v>1.5228</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2555</v>
+        <v>-0.4493</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7844</v>
+        <v>-0.0227</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5815</v>
+        <v>-0.2384</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2029</v>
+        <v>0.2158</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3452</v>
+        <v>0.1219</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5475</v>
+        <v>0.0409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2023</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4392</v>
+        <v>-0.1445</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.034</v>
+        <v>-0.2793</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4052</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9309</v>
+        <v>-0.0406</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8491</v>
+        <v>0.1823</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0818</v>
+        <v>-0.2229</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4539</v>
+        <v>0.9414</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7312</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6007</v>
+        <v>0.2377</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1589</v>
+        <v>-0.4179</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5583</v>
+        <v>0.6556</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0227</v>
+        <v>-1.8033</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2384</v>
+        <v>0.1517</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2158</v>
+        <v>-1.955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1219</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>0.7201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0809</v>
+        <v>-1.2801</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1445</v>
+        <v>-1.2433</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2793</v>
+        <v>-0.5684</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5134</v>
+        <v>0.7023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1816</v>
+        <v>0.635</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3318</v>
+        <v>0.0673</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9414</v>
+        <v>2.3154</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.712</v>
+        <v>-0.38</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8557</v>
+        <v>-1.581</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1437</v>
+        <v>1.201</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7439</v>
+        <v>-0.7844</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0698</v>
+        <v>-0.5815</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6741</v>
+        <v>-0.2029</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6741</v>
+        <v>-0.3452</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.5475</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>0.2023</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0698</v>
+        <v>-0.4392</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0698</v>
+        <v>-0.034</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.4052</v>
       </c>
       <c r="P8" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1634</v>
+        <v>0.663</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.6357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0182</v>
+        <v>0.0273</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.4539</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.737</v>
+        <v>-0.5837</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.984</v>
+        <v>-0.7546</v>
       </c>
       <c r="F9" t="n">
-        <v>0.247</v>
+        <v>0.1709</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8033</v>
+        <v>-0.7439</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1517</v>
+        <v>-0.0698</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.955</v>
+        <v>-0.6741</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.6741</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7201</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2801</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2433</v>
+        <v>-0.0698</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5684</v>
+        <v>-0.0698</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2724</v>
+        <v>-0.0351</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0689</v>
+        <v>-0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3412</v>
+        <v>0.0454</v>
       </c>
       <c r="V9" t="n">
-        <v>2.3154</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5372</v>
+        <v>-1.4712</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2885</v>
+        <v>-2.0863</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7513</v>
+        <v>0.6151</v>
       </c>
       <c r="G10" t="n">
         <v>0.1576</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1321</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>-0.0262</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5895</v>
+        <v>-2.36</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.24</v>
+        <v>-0.0378</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3495</v>
+        <v>-2.3222</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5611</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1772</v>
+        <v>0.0523</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U12" t="n">
-        <v>0.186</v>
+        <v>0.2132</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4373</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5621</v>
+        <v>-2.7043</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1081</v>
+        <v>-1.4409</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.454</v>
+        <v>-1.2634</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4793</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3284</v>
+        <v>-0.4705</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4205</v>
+        <v>-0.2299</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2898</v>
+        <v>8.592200000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>7.549300000000002</v>
+        <v>7.851999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7400999999999998</v>
+        <v>0.7402999999999997</v>
       </c>
       <c r="G14" t="n">
         <v>10.1134</v>
@@ -1546,13 +1546,13 @@
         <v>15.6272</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1415</v>
+        <v>1.4442</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7345</v>
+        <v>2.037</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5925</v>
+        <v>-0.5927</v>
       </c>
       <c r="V14" t="n">
         <v>0.9413</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1924</v>
+        <v>2.2275</v>
       </c>
       <c r="E15" t="n">
-        <v>2.197</v>
+        <v>2.0959</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0046</v>
+        <v>0.1316</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4394</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7236</v>
+        <v>-0.6885</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2337</v>
+        <v>-0.3349</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4898</v>
+        <v>-0.3536</v>
       </c>
       <c r="V15" t="n">
         <v>3.3787</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4206</v>
+        <v>1.4012</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3247</v>
+        <v>3.2236</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9041</v>
+        <v>-1.8224</v>
       </c>
       <c r="G16" t="n">
         <v>1.0751</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5178</v>
+        <v>-0.5372</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1594</v>
+        <v>-0.2606</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3583</v>
+        <v>-0.2766</v>
       </c>
       <c r="V16" t="n">
         <v>0.2772</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3849</v>
+        <v>0.5923</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7374000000000001</v>
+        <v>1.2144</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3525</v>
+        <v>-0.6222</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7117</v>
+        <v>-0.269</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.07829999999999999</v>
+        <v>1.3085</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6334</v>
+        <v>-1.5776</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0324</v>
+        <v>0.964</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0614</v>
+        <v>2.2717</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-1.3077</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6793</v>
+        <v>-1.233</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1397</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5397</v>
+        <v>-0.2698</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.624</v>
+        <v>0.1032</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4925</v>
+        <v>0.2504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1315</v>
+        <v>-0.1472</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.215</v>
+        <v>0.1282</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8099</v>
+        <v>0.5352</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5949</v>
+        <v>-0.407</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.269</v>
+        <v>-0.7117</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3085</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5776</v>
+        <v>-0.6334</v>
       </c>
       <c r="J18" t="n">
-        <v>0.964</v>
+        <v>-0.0324</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2717</v>
+        <v>0.0614</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3077</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.233</v>
+        <v>-0.6793</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.1397</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>-0.5397</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.274</v>
+        <v>0.3673</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.154</v>
+        <v>0.2903</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.12</v>
+        <v>0.077</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4407</v>
+        <v>-0.3825</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8915</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4509</v>
+        <v>0.2057</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8687</v>
@@ -1936,13 +1936,13 @@
         <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9394</v>
+        <v>-0.8811</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8335</v>
+        <v>-0.5302</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1058</v>
+        <v>-0.3509</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.4349</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0334</v>
+        <v>-0.3256</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0542</v>
+        <v>-0.1093</v>
       </c>
       <c r="G20" t="n">
         <v>0.5851</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0017</v>
+        <v>0.5427</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3961</v>
+        <v>0.3117</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3944</v>
+        <v>0.231</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1468</v>
+        <v>-1.321</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7575</v>
+        <v>0.4464</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3893</v>
+        <v>-1.7675</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0741</v>
+        <v>0.203</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.252</v>
+        <v>-1.766</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8221000000000001</v>
+        <v>1.969</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9709</v>
+        <v>2.1852</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.284</v>
+        <v>-0.3236</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6869</v>
+        <v>2.5089</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1032</v>
+        <v>-1.9822</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.968</v>
+        <v>-1.4423</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1352</v>
+        <v>-0.5399</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2279</v>
+        <v>-0.0199</v>
       </c>
       <c r="T21" t="n">
-        <v>0.831</v>
+        <v>0.3048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6031</v>
+        <v>-0.3247</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8317</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3132</v>
+        <v>-1.5356</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3453</v>
+        <v>-1.3641</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6585</v>
+        <v>-0.1714</v>
       </c>
       <c r="G22" t="n">
-        <v>0.203</v>
+        <v>-2.0741</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.766</v>
+        <v>-1.252</v>
       </c>
       <c r="I22" t="n">
-        <v>1.969</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1852</v>
+        <v>-0.9709</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3236</v>
+        <v>-0.284</v>
       </c>
       <c r="L22" t="n">
-        <v>2.5089</v>
+        <v>-0.6869</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9822</v>
+        <v>-1.1032</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4423</v>
+        <v>-0.968</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5399</v>
+        <v>-0.1352</v>
       </c>
       <c r="P22" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0121</v>
+        <v>-0.1609</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2037</v>
+        <v>0.2244</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2158</v>
+        <v>-0.3853</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4474</v>
+        <v>-1.8168</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0931</v>
+        <v>-1.5987</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3543</v>
+        <v>-0.2181</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8259</v>
@@ -2248,13 +2248,13 @@
         <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4017</v>
+        <v>0.0323</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6495</v>
+        <v>0.1439</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2477</v>
+        <v>-0.1116</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4614</v>
+        <v>-2.9476</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3885</v>
+        <v>-1.7929</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0729</v>
+        <v>-1.1547</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3784</v>
@@ -2326,13 +2326,13 @@
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9636</v>
+        <v>0.4774</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0115</v>
+        <v>-0.0702</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2186</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7137</v>
+        <v>-4.2003</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9905</v>
+        <v>-2.5861</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7232</v>
+        <v>-1.6142</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4094</v>
@@ -2404,13 +2404,13 @@
         <v>2.1488</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8903</v>
+        <v>-0.3769</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7592</v>
+        <v>-0.3548</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1311</v>
+        <v>-0.0221</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4373</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.2896</v>
+        <v>-8.2895</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7402000000000002</v>
+        <v>-0.7401000000000004</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.5492</v>
+        <v>-7.5495</v>
       </c>
       <c r="G26" t="n">
         <v>-10.1134</v>
@@ -2482,10 +2482,10 @@
         <v>19.5344</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1417</v>
+        <v>-1.1416</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5928999999999999</v>
+        <v>0.5926</v>
       </c>
       <c r="U26" t="n">
         <v>-1.7342</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484295_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484295_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9215</v>
+        <v>2.5391</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8142</v>
+        <v>1.4477</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8927</v>
+        <v>1.0914</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8511</v>
+        <v>2.3842</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2211</v>
+        <v>0.7391</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6301</v>
+        <v>1.6451</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0993</v>
+        <v>3.0835</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9291</v>
+        <v>0.4937</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1701</v>
+        <v>2.5898</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2482</v>
+        <v>-0.6994</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7081</v>
+        <v>0.2454</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5401</v>
+        <v>-0.9447</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7348</v>
+        <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.0789</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8722</v>
+        <v>0.1912</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9659</v>
+        <v>0.3454</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1542</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.067</v>
+        <v>-0.2316</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8279</v>
+        <v>0.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.895</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5391</v>
+        <v>2.3075</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4477</v>
+        <v>3.2002</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0914</v>
+        <v>-0.8927</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3842</v>
+        <v>4.2372</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7391</v>
+        <v>1.6071</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6451</v>
+        <v>2.6301</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0835</v>
+        <v>5.4853</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4937</v>
+        <v>2.3152</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5898</v>
+        <v>3.1701</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6994</v>
+        <v>-1.2482</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2454</v>
+        <v>-0.7081</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9447</v>
+        <v>-0.5401</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>-5.0789</v>
       </c>
       <c r="R4" t="n">
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1912</v>
+        <v>0.8722</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3454</v>
+        <v>0.9659</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1542</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2316</v>
+        <v>-0.067</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1675</v>
+        <v>1.8279</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3991</v>
+        <v>-1.895</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2377</v>
+        <v>0.614</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4179</v>
+        <v>0.614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6556</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8033</v>
+        <v>0.614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1517</v>
+        <v>0.614</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.955</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7201</v>
+        <v>0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2801</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2433</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5684</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7023</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0673</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3154</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.38</v>
+        <v>0.2377</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.581</v>
+        <v>-0.4179</v>
       </c>
       <c r="F8" t="n">
-        <v>1.201</v>
+        <v>0.6556</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7844</v>
+        <v>-1.8033</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5815</v>
+        <v>0.1517</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2029</v>
+        <v>-1.955</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3452</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5475</v>
+        <v>0.7201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2023</v>
+        <v>-1.2801</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4392</v>
+        <v>-1.2433</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.034</v>
+        <v>-0.5684</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4052</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.663</v>
+        <v>0.7023</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6357</v>
+        <v>0.635</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0273</v>
+        <v>0.0673</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4539</v>
+        <v>2.3154</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7312</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5837</v>
+        <v>-0.38</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7546</v>
+        <v>-1.581</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1709</v>
+        <v>1.201</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7439</v>
+        <v>-0.7844</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0698</v>
+        <v>-0.5815</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6741</v>
+        <v>-0.2029</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6741</v>
+        <v>-0.3452</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.5475</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>0.2023</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0698</v>
+        <v>-0.4392</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0698</v>
+        <v>-0.034</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.4052</v>
       </c>
       <c r="P9" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0351</v>
+        <v>0.663</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0805</v>
+        <v>0.6357</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0454</v>
+        <v>0.0273</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.4539</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4712</v>
+        <v>-0.5837</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0863</v>
+        <v>-0.7546</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6151</v>
+        <v>0.1709</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1576</v>
+        <v>-0.7439</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.112</v>
+        <v>-0.0698</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2696</v>
+        <v>-0.6741</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1023</v>
+        <v>-0.6741</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1023</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0553</v>
+        <v>-0.0698</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2144</v>
+        <v>-0.0698</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0351</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0399</v>
+        <v>-0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0262</v>
+        <v>0.0454</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.881</v>
+        <v>-1.4712</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9172</v>
+        <v>-2.0863</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9638</v>
+        <v>0.6151</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2012</v>
+        <v>0.1576</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7946</v>
+        <v>-0.112</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5934</v>
+        <v>0.2696</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4227</v>
+        <v>0.1023</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3057</v>
+        <v>0.1023</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6239</v>
+        <v>0.0553</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4889</v>
+        <v>-0.2144</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.135</v>
+        <v>0.2696</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5393</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3631</v>
+        <v>-0.0399</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1761</v>
+        <v>-0.0262</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.36</v>
+        <v>-1.881</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0378</v>
+        <v>-0.9172</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3222</v>
+        <v>-0.9638</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5611</v>
+        <v>-0.2012</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.372</v>
+        <v>-0.7946</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1891</v>
+        <v>0.5934</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1231</v>
+        <v>0.4227</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0422</v>
+        <v>-0.3057</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0.7284</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6842</v>
+        <v>-0.6239</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4142</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.27</v>
+        <v>-0.135</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0523</v>
+        <v>-0.5393</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1609</v>
+        <v>-0.3631</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2132</v>
+        <v>-0.1761</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7043</v>
+        <v>-2.36</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4409</v>
+        <v>-0.0378</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2634</v>
+        <v>-2.3222</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4793</v>
+        <v>-0.5611</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2231</v>
+        <v>-0.372</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2562</v>
+        <v>-0.1891</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5008</v>
+        <v>0.1231</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6498</v>
+        <v>0.0422</v>
       </c>
       <c r="L13" t="n">
-        <v>0.149</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9785</v>
+        <v>-0.6842</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5733</v>
+        <v>-0.4142</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4052</v>
+        <v>-0.27</v>
       </c>
       <c r="P13" t="n">
         <v>0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4705</v>
+        <v>0.0523</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2406</v>
+        <v>-0.1609</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2299</v>
+        <v>0.2132</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3405</v>
+        <v>-2.4373</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6177</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.592200000000002</v>
+        <v>-2.7043</v>
       </c>
       <c r="E14" t="n">
-        <v>7.851999999999999</v>
+        <v>-1.4409</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7402999999999997</v>
+        <v>-1.2634</v>
       </c>
       <c r="G14" t="n">
-        <v>10.1134</v>
+        <v>-1.4793</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7188</v>
+        <v>-1.2231</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3949</v>
+        <v>-0.2562</v>
       </c>
       <c r="J14" t="n">
-        <v>16.4289</v>
+        <v>-0.5008</v>
       </c>
       <c r="K14" t="n">
-        <v>7.657699999999999</v>
+        <v>-0.6498</v>
       </c>
       <c r="L14" t="n">
-        <v>8.770999999999997</v>
+        <v>0.149</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.315500000000001</v>
+        <v>-0.9785</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.9392</v>
+        <v>-0.5733</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.376300000000001</v>
+        <v>-0.4052</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.907</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.5343</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>15.6272</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4442</v>
+        <v>-0.4705</v>
       </c>
       <c r="T14" t="n">
-        <v>2.037</v>
+        <v>-0.2406</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5927</v>
+        <v>-0.2299</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9413</v>
+        <v>-1.3405</v>
       </c>
       <c r="W14" t="n">
-        <v>8.920200000000001</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.979</v>
+        <v>-1.6177</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2275</v>
+        <v>8.592200000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0959</v>
+        <v>7.851999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1316</v>
+        <v>0.7402999999999997</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4394</v>
+        <v>10.1135</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.846</v>
+        <v>4.7188</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5934</v>
+        <v>5.3949</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1385</v>
+        <v>16.4289</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1918</v>
+        <v>7.657799999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0533</v>
+        <v>8.770999999999997</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5779</v>
+        <v>-6.3155</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0379</v>
+        <v>-2.9392</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5401</v>
+        <v>-3.376300000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>-3.907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-19.53430000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>15.6272</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6885</v>
+        <v>1.4442</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3349</v>
+        <v>2.037</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3536</v>
+        <v>-0.5927</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3787</v>
+        <v>0.9413</v>
       </c>
       <c r="W15" t="n">
-        <v>3.269</v>
+        <v>8.920200000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1097</v>
-      </c>
+        <v>-7.979</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4012</v>
+        <v>2.2275</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2236</v>
+        <v>2.0959</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8224</v>
+        <v>0.1316</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0751</v>
+        <v>-1.4394</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7636</v>
+        <v>-0.846</v>
       </c>
       <c r="I16" t="n">
+        <v>-0.5934</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.5779</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1.0379</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.5401</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S16" t="n">
         <v>-0.6885</v>
       </c>
-      <c r="J16" t="n">
-        <v>2.7231</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.6017</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1214</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-1.648</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.838</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.8099</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.9534</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.5395</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.5372</v>
-      </c>
       <c r="T16" t="n">
-        <v>-0.2606</v>
+        <v>-0.3349</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2766</v>
+        <v>-0.3536</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>3.3787</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7145</v>
+        <v>3.269</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4373</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5923</v>
+        <v>1.4012</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2144</v>
+        <v>3.2236</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6222</v>
+        <v>-1.8224</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.269</v>
+        <v>1.0751</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3085</v>
+        <v>1.7636</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5776</v>
+        <v>-0.6885</v>
       </c>
       <c r="J17" t="n">
-        <v>0.964</v>
+        <v>2.7231</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2717</v>
+        <v>2.6017</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3077</v>
+        <v>0.1214</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.233</v>
+        <v>-1.648</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.838</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2698</v>
+        <v>-0.8099</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1032</v>
+        <v>-0.5372</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2504</v>
+        <v>-0.2606</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1472</v>
+        <v>-0.2766</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1282</v>
+        <v>0.607</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5352</v>
+        <v>0.607</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.407</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7117</v>
+        <v>0.607</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6334</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0324</v>
+        <v>0.607</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6793</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1397</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3673</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2903</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3825</v>
+        <v>0.5923</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5881999999999999</v>
+        <v>1.2144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2057</v>
+        <v>-0.6222</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8687</v>
+        <v>-0.269</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8547</v>
+        <v>1.3085</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.014</v>
+        <v>-1.5776</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1141</v>
+        <v>0.964</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2213</v>
+        <v>2.2717</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3354</v>
+        <v>-1.3077</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9828</v>
+        <v>-1.233</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6334</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3494</v>
+        <v>-0.2698</v>
       </c>
       <c r="P19" t="n">
         <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8811</v>
+        <v>0.1032</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5302</v>
+        <v>0.2504</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3509</v>
+        <v>-0.1472</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4349</v>
+        <v>0.1282</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3256</v>
+        <v>0.5352</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1093</v>
+        <v>-0.407</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5851</v>
+        <v>-0.7117</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5477</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1328</v>
+        <v>-0.6334</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2928</v>
+        <v>-0.0324</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3505</v>
+        <v>0.0614</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9424</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7077</v>
+        <v>-0.6793</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8982</v>
+        <v>-0.1397</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8095</v>
+        <v>-0.5397</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5427</v>
+        <v>0.3673</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3117</v>
+        <v>0.2903</v>
       </c>
       <c r="U20" t="n">
-        <v>0.231</v>
+        <v>0.077</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.321</v>
+        <v>-0.3825</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4464</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7675</v>
+        <v>0.2057</v>
       </c>
       <c r="G21" t="n">
-        <v>0.203</v>
+        <v>-0.8687</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.766</v>
+        <v>-0.8547</v>
       </c>
       <c r="I21" t="n">
-        <v>1.969</v>
+        <v>-0.014</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1852</v>
+        <v>1.1141</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3236</v>
+        <v>-0.2213</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5089</v>
+        <v>1.3354</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9822</v>
+        <v>-1.9828</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4423</v>
+        <v>-0.6334</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5399</v>
+        <v>-1.3494</v>
       </c>
       <c r="P21" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0199</v>
+        <v>-0.8811</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3048</v>
+        <v>-0.5302</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3247</v>
+        <v>-0.3509</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5356</v>
+        <v>-1.0419</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3641</v>
+        <v>-0.9326</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1714</v>
+        <v>-0.1093</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0741</v>
+        <v>-0.0219</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.252</v>
+        <v>-0.5477</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8221000000000001</v>
+        <v>0.5259</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9709</v>
+        <v>1.6858</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.284</v>
+        <v>0.3505</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6869</v>
+        <v>1.3354</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1032</v>
+        <v>-1.7077</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.968</v>
+        <v>-0.8982</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1352</v>
+        <v>-0.8095</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1609</v>
+        <v>0.5427</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2244</v>
+        <v>0.3117</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3853</v>
+        <v>0.231</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. EXPOSITO FORTUNY</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8168</v>
+        <v>-1.321</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5987</v>
+        <v>0.4464</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2181</v>
+        <v>-1.7675</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8259</v>
+        <v>0.203</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8703</v>
+        <v>-1.766</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9556</v>
+        <v>1.969</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8478</v>
+        <v>2.1852</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9159</v>
+        <v>-0.3236</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06809999999999999</v>
+        <v>2.5089</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9781</v>
+        <v>-1.9822</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0456</v>
+        <v>-1.4423</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0237</v>
+        <v>-0.5399</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0323</v>
+        <v>-0.0199</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1439</v>
+        <v>0.3048</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1116</v>
+        <v>-0.3247</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9476</v>
+        <v>-1.5356</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7929</v>
+        <v>-1.3641</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1547</v>
+        <v>-0.1714</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3784</v>
+        <v>-2.0741</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.9601</v>
+        <v>-1.252</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4183</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1452</v>
+        <v>-0.9709</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2666</v>
+        <v>-0.284</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1214</v>
+        <v>-0.6869</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2332</v>
+        <v>-1.1032</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6935</v>
+        <v>-0.968</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5397</v>
+        <v>-0.1352</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4774</v>
+        <v>-0.1609</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5476</v>
+        <v>0.2244</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0702</v>
+        <v>-0.3853</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. EXPOSITO FORTUNY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2003</v>
+        <v>-1.8168</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5861</v>
+        <v>-1.5987</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6142</v>
+        <v>-0.2181</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4094</v>
+        <v>-2.8259</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3843</v>
+        <v>-0.8703</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7937</v>
+        <v>-1.9556</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8942</v>
+        <v>-0.8478</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4735</v>
+        <v>-0.9159</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5794</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3036</v>
+        <v>-1.9781</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0893</v>
+        <v>0.0456</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2144</v>
+        <v>-2.0237</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9767</v>
+        <v>0.9767</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R25" t="n">
         <v>2.1488</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3769</v>
+        <v>0.0323</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3548</v>
+        <v>0.1439</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0221</v>
+        <v>-0.1116</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-2.9476</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.7929</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.1547</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.3784</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.9601</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4183</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.1452</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.2666</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.2332</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6935</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5397</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.0702</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C. MARZO CHECA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.2003</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.5861</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.6142</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.3843</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.7937</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8942</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.4735</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.5794</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.3036</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.0893</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.2144</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.3769</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.3548</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484295_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-8.2895</v>
       </c>
-      <c r="E26" t="n">
-        <v>-0.7401000000000004</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E28" t="n">
+        <v>-0.7401000000000013</v>
+      </c>
+      <c r="F28" t="n">
         <v>-7.5495</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>-10.1134</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H28" t="n">
         <v>-4.7187</v>
       </c>
-      <c r="I26" t="n">
-        <v>-5.3948</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="I28" t="n">
+        <v>-5.394699999999999</v>
+      </c>
+      <c r="J28" t="n">
         <v>6.3156</v>
       </c>
-      <c r="K26" t="n">
-        <v>2.9392</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K28" t="n">
+        <v>2.939200000000001</v>
+      </c>
+      <c r="L28" t="n">
         <v>3.3765</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>-16.429</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>-7.6579</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>-8.7713</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>3.9068</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-15.6274</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>19.5344</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>-1.1416</v>
       </c>
-      <c r="T26" t="n">
-        <v>0.5926</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T28" t="n">
+        <v>0.5926000000000001</v>
+      </c>
+      <c r="U28" t="n">
         <v>-1.7342</v>
       </c>
-      <c r="V26" t="n">
-        <v>-0.9413999999999998</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="V28" t="n">
+        <v>-0.9414000000000002</v>
+      </c>
+      <c r="W28" t="n">
         <v>7.978899999999999</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-8.920299999999999</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
